--- a/etf_holdings/2026-10-29_00407A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-29_00407A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:28</t>
+          <t>2026-10-29 23:21:42</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+1.04%2425</t>
+          <t>-0.41%2415</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+1.04%</t>
+          <t>-0.41%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2425</v>
+        <v>2415</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>9.42%830,000</t>
+          <t>9.66%830,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>9.42%</t>
+          <t>9.66%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:28</t>
+          <t>2026-10-29 23:21:42</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,25 +570,25 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>+3.77%1100</t>
+          <t>-5.45%1040</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>+3.77%</t>
+          <t>-5.45%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1100</v>
+        <v>1040</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6.16%1,197,000</t>
+          <t>6.00%1,197,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6.16%</t>
+          <t>6.00%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.23%</t>
+          <t>-0.34%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:28</t>
+          <t>2026-10-29 23:21:42</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -626,38 +626,38 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>3017奇鋐</t>
+          <t>2383台光電</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+2.72%3215</t>
+          <t>-0.3%5010</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+2.72%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3215</v>
+        <v>5010</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5.64%375,000</t>
+          <t>5.75%238,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.64%</t>
+          <t>5.75%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>375000</v>
+        <v>238000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.16%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:28</t>
+          <t>2026-10-29 23:21:42</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -687,38 +687,38 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2383台光電</t>
+          <t>3017奇鋐</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+5.79%5025</t>
+          <t>-3.42%3105</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+5.79%</t>
+          <t>-3.42%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>5025</v>
+        <v>3105</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.60%238,000</t>
+          <t>5.61%375,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.60%</t>
+          <t>5.61%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>238000</v>
+        <v>375000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.32%</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:28</t>
+          <t>2026-10-29 23:21:42</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,25 +753,25 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+6.94%4235</t>
+          <t>-4.49%4045</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+6.94%</t>
+          <t>-4.49%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>4235</v>
+        <v>4045</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5.33%269,000</t>
+          <t>5.25%269,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.33%</t>
+          <t>5.25%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.36%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:28</t>
+          <t>2026-10-29 23:21:42</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,25 +814,25 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+9.96%8170</t>
+          <t>-6.49%7640</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+9.96%</t>
+          <t>-6.49%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>8170</v>
+        <v>7640</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4.89%128,000</t>
+          <t>4.71%128,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4.89%</t>
+          <t>4.71%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.46%</t>
+          <t>-0.32%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:28</t>
+          <t>2026-10-29 23:21:42</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,25 +875,25 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+3.59%1300</t>
+          <t>-3.85%1250</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+3.59%</t>
+          <t>-3.85%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1300</v>
+        <v>1250</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.70%608,000</t>
+          <t>3.66%608,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3.70%</t>
+          <t>3.66%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:28</t>
+          <t>2026-10-29 23:21:42</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,25 +936,25 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+8.79%6375</t>
+          <t>+0.47%6405</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+8.79%</t>
+          <t>+0.47%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>6375</v>
+        <v>6405</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.46%116,000</t>
+          <t>3.58%116,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3.46%</t>
+          <t>3.58%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.29%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:28</t>
+          <t>2026-10-29 23:21:42</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,25 +997,25 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+6.76%695</t>
+          <t>-1.73%683</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+6.76%</t>
+          <t>-1.73%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>695</v>
+        <v>683</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.10%952,000</t>
+          <t>3.13%952,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3.10%</t>
+          <t>3.13%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.21%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:28</t>
+          <t>2026-10-29 23:21:42</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,25 +1058,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+7.23%319</t>
+          <t>-2.19%312</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+7.23%</t>
+          <t>-2.19%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.98%1,995,000</t>
+          <t>3.00%1,995,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2.98%</t>
+          <t>3.00%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.21%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:28</t>
+          <t>2026-10-29 23:21:42</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,25 +1119,25 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0%1950</t>
+          <t>-3.33%1885</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-3.33%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1950</v>
+        <v>1885</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.44%267,644</t>
+          <t>2.43%267,644</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2.44%</t>
+          <t>2.43%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:28</t>
+          <t>2026-10-29 23:21:42</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>2327國巨*</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+4.32%1810</t>
+          <t>-0.73%543</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+4.32%</t>
+          <t>-0.73%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1810</v>
+        <v>543</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.36%278,000</t>
+          <t>2.34%895,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.36%</t>
+          <t>2.34%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>278000</v>
+        <v>895000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:28</t>
+          <t>2026-10-29 23:21:42</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,25 +1241,25 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+2.65%1550</t>
+          <t>-4.52%1480</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+2.65%</t>
+          <t>-4.52%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1550</v>
+        <v>1480</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.34%323,000</t>
+          <t>2.30%323,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.34%</t>
+          <t>2.30%</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:28</t>
+          <t>2026-10-29 23:21:42</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2327國巨*</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+4.99%547</t>
+          <t>-5.8%1705</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+4.99%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>547</v>
+        <v>1705</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.29%895,000</t>
+          <t>2.28%278,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.29%</t>
+          <t>2.28%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>895000</v>
+        <v>278000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:28</t>
+          <t>2026-10-29 23:21:42</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,25 +1363,25 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+6.78%5115</t>
+          <t>-5.38%4840</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+6.78%</t>
+          <t>-5.38%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>5115</v>
+        <v>4840</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.25%94,000</t>
+          <t>2.19%94,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.25%</t>
+          <t>2.19%</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:29</t>
+          <t>2026-10-29 23:21:44</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,25 +1424,25 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+7.42%1375</t>
+          <t>+1.09%1390</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+7.42%</t>
+          <t>+1.09%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1375</v>
+        <v>1390</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.99%309,000</t>
+          <t>2.07%309,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>1.99%</t>
+          <t>2.07%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:29</t>
+          <t>2026-10-29 23:21:44</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1485,25 +1485,25 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+3.47%10150</t>
+          <t>-2.66%9880</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+3.47%</t>
+          <t>-2.66%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>10150</v>
+        <v>9880</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.90%40,000</t>
+          <t>1.91%40,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.90%</t>
+          <t>1.91%</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:29</t>
+          <t>2026-10-29 23:21:44</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,38 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2368金像電</t>
+          <t>3081聯亞</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+9.72%1185</t>
+          <t>-0.19%2575</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+9.72%</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>1185</v>
+        <v>2575</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.86%335,000</t>
+          <t>1.90%153,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.86%</t>
+          <t>1.90%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>335000</v>
+        <v>153000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:29</t>
+          <t>2026-10-29 23:21:44</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,38 +1602,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>3081聯亞</t>
+          <t>5274信驊</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+3.2%2580</t>
+          <t>-1.82%16980</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+3.2%</t>
+          <t>-1.82%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>2580</v>
+        <v>16980</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.85%153,000</t>
+          <t>1.87%22,900</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.85%</t>
+          <t>1.87%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>153000</v>
+        <v>22900</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:29</t>
+          <t>2026-10-29 23:21:44</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>5274信驊</t>
+          <t>2368金像電</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+7.99%17295</t>
+          <t>-5.91%1115</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+7.99%</t>
+          <t>-5.91%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>17295</v>
+        <v>1115</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.85%22,900</t>
+          <t>1.80%335,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.85%</t>
+          <t>1.80%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>22900</v>
+        <v>335000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:29</t>
+          <t>2026-10-29 23:21:44</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,38 +1724,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>6187萬潤</t>
+          <t>2408南亞科</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+4.67%1345</t>
+          <t>0%477</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+4.67%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1345</v>
+        <v>477</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.61%255,000</t>
+          <t>1.62%706,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.61%</t>
+          <t>1.62%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>255000</v>
+        <v>706000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:29</t>
+          <t>2026-10-29 23:21:44</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1785,38 +1785,38 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2408南亞科</t>
+          <t>6187萬潤</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+8.16%477</t>
+          <t>-6.32%1260</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+8.16%</t>
+          <t>-6.32%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>477</v>
+        <v>1260</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.58%706,000</t>
+          <t>1.55%255,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.58%</t>
+          <t>1.55%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>706000</v>
+        <v>255000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:29</t>
+          <t>2026-10-29 23:21:44</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,38 +1846,38 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3008大立光</t>
+          <t>2345智邦</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+5.58%6335</t>
+          <t>-3.31%1755</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+5.58%</t>
+          <t>-3.31%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>6335</v>
+        <v>1755</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.54%52,000</t>
+          <t>1.52%180,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.54%</t>
+          <t>1.52%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>52000</v>
+        <v>180000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:29</t>
+          <t>2026-10-29 23:21:44</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,38 +1907,38 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>3008大立光</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+3.13%1815</t>
+          <t>-8.21%5815</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+3.13%</t>
+          <t>-8.21%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1815</v>
+        <v>5815</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.53%180,000</t>
+          <t>1.46%52,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.53%</t>
+          <t>1.46%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>180000</v>
+        <v>52000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:29</t>
+          <t>2026-10-29 23:21:44</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1973,25 +1973,25 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+3.56%261.5</t>
+          <t>-3.63%252</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+3.56%</t>
+          <t>-3.63%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>261.5</v>
+        <v>252</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.42%1,160,000</t>
+          <t>1.41%1,160,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>1.41%</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:29</t>
+          <t>2026-10-29 23:21:44</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>6510精測</t>
+          <t>8996高力</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+9.97%3200</t>
+          <t>-2.52%1545</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+9.97%</t>
+          <t>-2.52%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>3200</v>
+        <v>1545</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.42%95,000</t>
+          <t>1.33%179,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.42%</t>
+          <t>1.33%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>95000</v>
+        <v>179000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:29</t>
+          <t>2026-10-29 23:21:44</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,38 +2090,38 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>8996高力</t>
+          <t>6510精測</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+8.19%1585</t>
+          <t>-10%2880</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+8.19%</t>
+          <t>-10%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>1585</v>
+        <v>2880</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.33%179,000</t>
+          <t>1.32%95,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1.33%</t>
+          <t>1.32%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>179000</v>
+        <v>95000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:29</t>
+          <t>2026-10-29 23:21:44</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2156,25 +2156,25 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>+9.33%2460</t>
+          <t>-1.42%2425</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+9.33%</t>
+          <t>-1.42%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>2460</v>
+        <v>2425</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.29%112,000</t>
+          <t>1.31%112,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1.29%</t>
+          <t>1.31%</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:29</t>
+          <t>2026-10-29 23:21:44</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2217,16 +2217,16 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+2.1%194.5</t>
+          <t>-3.08%188.5</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+2.1%</t>
+          <t>-3.08%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>194.5</v>
+        <v>188.5</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:29</t>
+          <t>2026-10-29 23:21:44</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2278,25 +2278,25 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+5.77%550</t>
+          <t>-5.45%520</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+5.77%</t>
+          <t>-5.45%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>550</v>
+        <v>520</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.08%418,000</t>
+          <t>1.05%418,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1.08%</t>
+          <t>1.05%</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -2304,7 +2304,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:31</t>
+          <t>2026-10-29 23:21:45</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2339,16 +2339,16 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+9.86%914</t>
+          <t>-2.84%888</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+9.86%</t>
+          <t>-2.84%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>914</v>
+        <v>888</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:31</t>
+          <t>2026-10-29 23:21:45</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2400,16 +2400,16 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+1.72%118.5</t>
+          <t>-2.95%115</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+1.72%</t>
+          <t>-2.95%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>118.5</v>
+        <v>115</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:31</t>
+          <t>2026-10-29 23:21:45</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2461,25 +2461,25 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>+4.09%2035</t>
+          <t>-4.42%1945</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+4.09%</t>
+          <t>-4.42%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>2035</v>
+        <v>1945</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.00%105,000</t>
+          <t>0.98%105,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>1.00%</t>
+          <t>0.98%</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:31</t>
+          <t>2026-10-29 23:21:45</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2522,16 +2522,16 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+1.56%1955</t>
+          <t>-2.81%1900</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+1.56%</t>
+          <t>-2.81%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1955</v>
+        <v>1900</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:31</t>
+          <t>2026-10-29 23:21:45</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2583,25 +2583,25 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-0.17%598</t>
+          <t>-0.33%596</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>-0.33%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.85%302,000</t>
+          <t>0.87%302,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.87%</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:31</t>
+          <t>2026-10-29 23:21:45</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2644,25 +2644,25 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+5.1%1340</t>
+          <t>-3.73%1290</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+5.1%</t>
+          <t>-3.73%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>1340</v>
+        <v>1290</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.85%135,000</t>
+          <t>0.84%135,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.84%</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:31</t>
+          <t>2026-10-29 23:21:45</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,25 +2705,25 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>+3.23%2080</t>
+          <t>-3.85%2000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+3.23%</t>
+          <t>-3.85%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>2080</v>
+        <v>2000</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.78%80,000</t>
+          <t>0.77%80,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>0.77%</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:31</t>
+          <t>2026-10-29 23:21:45</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,25 +2766,25 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+0.5%800</t>
+          <t>+1%808</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+0.5%</t>
+          <t>+1%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>800</v>
+        <v>808</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.64%171,000</t>
+          <t>0.67%171,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.64%</t>
+          <t>0.67%</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:31</t>
+          <t>2026-10-29 23:21:45</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,25 +2827,25 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+4.49%128</t>
+          <t>-9.77%115.5</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+4.49%</t>
+          <t>-9.77%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>128</v>
+        <v>115.5</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.53%878,000</t>
+          <t>0.49%878,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.53%</t>
+          <t>0.49%</t>
         </is>
       </c>
       <c r="K40" t="n">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:31</t>
+          <t>2026-10-29 23:21:45</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,25 +2888,25 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+3.7%224</t>
+          <t>-4.69%213.5</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+3.7%</t>
+          <t>-4.69%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>224</v>
+        <v>213.5</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.42%400,000</t>
+          <t>0.41%400,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.42%</t>
+          <t>0.41%</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:31</t>
+          <t>2026-10-29 23:21:45</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,25 +2949,25 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+4.26%293.5</t>
+          <t>+0.17%294</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+4.26%</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>293.5</v>
+        <v>294</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.35%252,000</t>
+          <t>0.36%252,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.35%</t>
+          <t>0.36%</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -2975,7 +2975,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:31</t>
+          <t>2026-10-29 23:21:45</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3010,25 +3010,25 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+0.84%1200</t>
+          <t>+3.33%1240</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+0.84%</t>
+          <t>+3.33%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>1200</v>
+        <v>1240</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.33%59,000</t>
+          <t>0.35%59,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.33%</t>
+          <t>0.35%</t>
         </is>
       </c>
       <c r="K43" t="n">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:31</t>
+          <t>2026-10-29 23:21:45</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3071,25 +3071,25 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>+6.81%2040</t>
+          <t>+0.49%2050</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>+6.81%</t>
+          <t>+0.49%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>2040</v>
+        <v>2050</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.32%34,000</t>
+          <t>0.34%34,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>0.34%</t>
         </is>
       </c>
       <c r="K44" t="n">
@@ -3097,7 +3097,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:31</t>
+          <t>2026-10-29 23:21:45</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3132,25 +3132,25 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+9.98%363.5</t>
+          <t>-0.41%362</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+9.98%</t>
+          <t>-0.41%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>363.5</v>
+        <v>362</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.30%176,828</t>
+          <t>0.31%176,828</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.31%</t>
         </is>
       </c>
       <c r="K45" t="n">
@@ -3158,7 +3158,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:31</t>
+          <t>2026-10-29 23:21:45</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3193,25 +3193,25 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>+3.56%843</t>
+          <t>-0.24%841</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>+3.56%</t>
+          <t>-0.24%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.30%77,000</t>
+          <t>0.31%77,000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.31%</t>
         </is>
       </c>
       <c r="K46" t="n">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:32</t>
+          <t>2026-10-29 23:21:46</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3254,16 +3254,16 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-0.25%791</t>
+          <t>+0.38%794</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-0.25%</t>
+          <t>+0.38%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:32</t>
+          <t>2026-10-29 23:21:46</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3310,38 +3310,38 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>3529力旺</t>
+          <t>3406玉晶光</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>+5.57%2655</t>
+          <t>-9.77%1200</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>+5.57%</t>
+          <t>-9.77%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>2655</v>
+        <v>1200</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0.22%18,000</t>
+          <t>0.26%45,000</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>0.22%</t>
+          <t>0.26%</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>18000</v>
+        <v>45000</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:32</t>
+          <t>2026-10-29 23:21:46</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3376,16 +3376,16 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>+2.56%560</t>
+          <t>-1.61%551</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>+2.56%</t>
+          <t>-1.61%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>560</v>
+        <v>551</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:32</t>
+          <t>2026-10-29 23:21:46</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3437,16 +3437,16 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>+5.52%172</t>
+          <t>-0.87%170.5</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>+5.52%</t>
+          <t>-0.87%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>172</v>
+        <v>170.5</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-29 00:05:32</t>
+          <t>2026-10-29 23:21:46</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3498,16 +3498,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>0%1140</t>
+          <t>+0.88%1150</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+0.88%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>1140</v>
+        <v>1150</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>

--- a/etf_holdings/2026-10-29_00407A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-29_00407A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:42</t>
+          <t>2026-10-29 23:34:41</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:42</t>
+          <t>2026-10-29 23:34:41</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:42</t>
+          <t>2026-10-29 23:34:41</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:42</t>
+          <t>2026-10-29 23:34:41</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:42</t>
+          <t>2026-10-29 23:34:41</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:42</t>
+          <t>2026-10-29 23:34:41</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:42</t>
+          <t>2026-10-29 23:34:41</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:42</t>
+          <t>2026-10-29 23:34:41</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:42</t>
+          <t>2026-10-29 23:34:41</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:42</t>
+          <t>2026-10-29 23:34:41</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:42</t>
+          <t>2026-10-29 23:34:41</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:42</t>
+          <t>2026-10-29 23:34:41</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:42</t>
+          <t>2026-10-29 23:34:41</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:42</t>
+          <t>2026-10-29 23:34:41</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:42</t>
+          <t>2026-10-29 23:34:41</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:44</t>
+          <t>2026-10-29 23:34:43</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:44</t>
+          <t>2026-10-29 23:34:43</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:44</t>
+          <t>2026-10-29 23:34:43</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:44</t>
+          <t>2026-10-29 23:34:43</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:44</t>
+          <t>2026-10-29 23:34:43</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:44</t>
+          <t>2026-10-29 23:34:43</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:44</t>
+          <t>2026-10-29 23:34:43</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:44</t>
+          <t>2026-10-29 23:34:43</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:44</t>
+          <t>2026-10-29 23:34:43</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:44</t>
+          <t>2026-10-29 23:34:43</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:44</t>
+          <t>2026-10-29 23:34:43</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:44</t>
+          <t>2026-10-29 23:34:43</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:44</t>
+          <t>2026-10-29 23:34:43</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:44</t>
+          <t>2026-10-29 23:34:43</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:44</t>
+          <t>2026-10-29 23:34:43</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:45</t>
+          <t>2026-10-29 23:34:44</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:45</t>
+          <t>2026-10-29 23:34:44</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:45</t>
+          <t>2026-10-29 23:34:44</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:45</t>
+          <t>2026-10-29 23:34:44</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:45</t>
+          <t>2026-10-29 23:34:44</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:45</t>
+          <t>2026-10-29 23:34:44</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:45</t>
+          <t>2026-10-29 23:34:44</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:45</t>
+          <t>2026-10-29 23:34:44</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:45</t>
+          <t>2026-10-29 23:34:44</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:45</t>
+          <t>2026-10-29 23:34:44</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:45</t>
+          <t>2026-10-29 23:34:44</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:45</t>
+          <t>2026-10-29 23:34:44</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:45</t>
+          <t>2026-10-29 23:34:44</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:45</t>
+          <t>2026-10-29 23:34:44</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:45</t>
+          <t>2026-10-29 23:34:44</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:46</t>
+          <t>2026-10-29 23:34:45</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:46</t>
+          <t>2026-10-29 23:34:45</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:46</t>
+          <t>2026-10-29 23:34:45</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:46</t>
+          <t>2026-10-29 23:34:45</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-29 23:21:46</t>
+          <t>2026-10-29 23:34:45</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
